--- a/test/excel/xlsx/roundtrip/values.xlsx
+++ b/test/excel/xlsx/roundtrip/values.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fxlsx-71511/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fxlsx-96170/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5275EB36-9736-9341-834A-8F5586B90D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44BE0478-9EFE-B34E-9D9A-84A30DB4E0ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>text</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>'apostrophe first</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>x</t>
@@ -436,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
@@ -528,7 +531,7 @@
         <v>6</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -544,6 +547,11 @@
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/test/excel/xlsx/roundtrip/values.xlsx
+++ b/test/excel/xlsx/roundtrip/values.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fxlsx-96170/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fxlsx-67743/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44BE0478-9EFE-B34E-9D9A-84A30DB4E0ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BFFA519-1542-1449-A736-8F2769BE9A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
